--- a/protocolo_pruebas_WIP_v2_c.xlsx
+++ b/protocolo_pruebas_WIP_v2_c.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LAC\2026\Sebastian\Tesis_pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CCC152-0063-48BE-A5CB-8C363685A77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB03F63E-D935-48CE-91A5-F066E890441A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63CCC3CA-1558-461E-B0B6-AA37C2AD9662}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{63CCC3CA-1558-461E-B0B6-AA37C2AD9662}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fase Simulacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Fase 1 Simulacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Fase 2 Enulación" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +39,70 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="5">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="5">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="148">
   <si>
     <t>Numero de Prueba</t>
   </si>
@@ -219,9 +282,6 @@
   </si>
   <si>
     <t>TRABAJO DE GRADO PARA OPTAR POR EL TÍTULO DE INGENIERO EN REDES Y TELECOMUNICACIONES</t>
-  </si>
-  <si>
-    <t>Protocolo de Pruebas y Resultados</t>
   </si>
   <si>
     <r>
@@ -378,12 +438,367 @@
   <si>
     <t>Verificación de escalación de privilegios</t>
   </si>
+  <si>
+    <t>Protocolo de Pruebas y Resultados Fase 2: Laboratorio Físico</t>
+  </si>
+  <si>
+    <t>Protocolo de Pruebas y Resultados Fase 1: Laboratorio Virtual</t>
+  </si>
+  <si>
+    <t>Fecha: Junio del 2026</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.192.0.1:  PCwin11-1</t>
+  </si>
+  <si>
+    <t>Destino: 192.192.0.1
+Comando: ping 192.192.0.1</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.192.0.1:  PCwin11-2</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.192.0.1:  PCwin11-3</t>
+  </si>
+  <si>
+    <t>Destino: 192.168.10.1.
+Comando: ping 192.168.10.1</t>
+  </si>
+  <si>
+    <t>Verificar la conectividad ICMP desde cada host de la LAN interna hacia la interfaz Switch (Catalyst 2960).</t>
+  </si>
+  <si>
+    <t>Desde PCwin11-1/2/3 hast  puerto del switch</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.168.10.1:  PCwin11-1</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.168.10.1:  PCwin11-2</t>
+  </si>
+  <si>
+    <t>Respuerta desde 192.168.10.1:  PCwin11-3</t>
+  </si>
+  <si>
+    <t>Verificar la conectividad ICMP desde cada host de la LAN interna hacia la interfaz del equipo Internet Service.</t>
+  </si>
+  <si>
+    <t>Desde PCwin11-1/2/3 hast  Internet Service</t>
+  </si>
+  <si>
+    <t>Destino: 200.50.10.10
+Comando: ping  200.50.10.10</t>
+  </si>
+  <si>
+    <t>Respuerta desde  200.50.10.10:  PCwin11-1</t>
+  </si>
+  <si>
+    <t>Respuerta desde  200.50.10.10:  PCwin11-2</t>
+  </si>
+  <si>
+    <t>Respuerta desde  200.50.10.10:  PCwin11-3</t>
+  </si>
+  <si>
+    <t>Desde la consola del DockerServer hasta los contenedores.</t>
+  </si>
+  <si>
+    <t>Verificar que todos los servicios del stack están desplegados y en ejecución dentro del entorno Docker.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">En la terminal del Docker Server se ejecuta el comando:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">dps
+(alias del comando docker ps -a)
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Listado con las aplicaciones activas en Docker.</t>
+  </si>
+  <si>
+    <t>Verificar que zuricata  esté activo</t>
+  </si>
+  <si>
+    <t>Desde una terminal en el servidor hasta la respuesta de la aplicación</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">en la terminal de Docker Server se ejecuta el comando:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sudo systemctl status suricata.service</t>
+    </r>
+  </si>
+  <si>
+    <t>Active: active (running) since &lt;fecha y hora&gt;</t>
+  </si>
+  <si>
+    <t>Desde el PCWin11 - 1 hasta el servidor.</t>
+  </si>
+  <si>
+    <t>Como Administrador en el PCW11-1 (10.0.2.15)
+Escanear puertos del servidor y otras estaciones
+nmap -sS -p 1-1000 -T5 192.168.0.1
+nmap -sS -p 1-1000 -T5 192.168.0.95
+nmap -sS -p 1-1000 -T5 192.168.0.57</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Escaneo de Red (Activación R1, R2, R4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)
+Demostrar que el sistema detecta actividades de reconocimiento (mapeo de red) desde una estación Windows</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fuerza Bruta SSH (Activación R3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Demostrar que el sistema detecta intentos de acceso no autorizado por SSH desde una estación Windows.</t>
+    </r>
+  </si>
+  <si>
+    <t>Desde PCW11-2  hasta el servidor.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instalar sshpass o usar WSL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2.	Intentar conexiones SSH con contraseñas incorrectas
+ssh usuario_inexistente@192.168.0.10
+ssh root@192.168.0.10
+ssh admin@192.168.0.10
+Repetir al menos 10 veces con diferentes usuarios
+for ($i=0; $i -le 10; $i++) {  ssh test$i@192.168.0.10}
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Movimiento Lateral (Activación R5, R6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)
+Demostrar que el sistema detecta ejecución remota de comandos desde una estación comprometida hacia otra.</t>
+    </r>
+  </si>
+  <si>
+    <t>Desde PCW11-1 hacia PCW11-3</t>
+  </si>
+  <si>
+    <t>PCW11 - 1 
+Ejecutar comandos remotos en w3 (10.0.2.25)
+1.	Si tiene SSH habilitado en Windows:
+ssh win3@10.0.2.25 "whoami &amp;&amp; hostname &amp;&amp; ipconfig"
+2.	o usando PsExec (herramienta de Sysinternals)
+.\PsExec.exe \\10.0.2.25 -u win3 cmd /c "whoami"
+Acción desde w2 hacia Servidor
+Powershell: como Administrador en w2 (10.0.2.20)
+Múltiples conexiones SSH al servidor
+ssh win1@192.168.0.10 "ls -la /etc/"
+ssh win1@192.168.0.10 "cat /var/log/auth.log"
+ssh win1@192.168.0.10 "whoami"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Escalación de Privilegios (Activación R5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Demostrar que el sistema detecta intentos de escalar privilegios en una estación Windows.</t>
+    </r>
+  </si>
+  <si>
+    <t>Desde PCW11-3 hacia el servidor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. 	Ver privilegios actuales
+whoami /priv
+2. 	Intentar agregar usuario al grupo Administradores
+net localgroup Administradores usuario_prueba /add
+3. 	Crear persistencia en registro
+Reg add "HKLM\SOFTWARE\Microsoft\Windows\CurrentVersion\Run" /v TestTesis /t REG_SZ /d "C:\Users\Public\malware.exe" /f
+4. 	Crear servicio malicioso
+sc create ServicioTesis binPath= "C:\Users\Public\malware.exe" start= auto
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ataque Combinado (Activación R6 - La más importante)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Demostrar la correlación multi-fase (R6) combinando escaneo de red + fuerza bruta SSH.</t>
+    </r>
+  </si>
+  <si>
+    <t>Acción coordinada desde PCW11_1 y PCW11-2 hacia el Servidor</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fase 1 - Reconocimiento PCW11-1:
+PCW11-1 escanea la red
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nmap -sS -p 1-1000 -T5 10.0.2.0/24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Fase 2 - Acceso inicial PCW11-2 - Inmediatamente después intenta fuerza bruta SSH contra el servidor
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>for ($i=0; $i -le 15; $i++) { ssh usuario$i@192.168.0.10 }</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,8 +837,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,8 +872,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -586,12 +1022,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -603,67 +1113,139 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -731,6 +1313,139 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>63501</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3473</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAB33642-7306-4FF9-8D1F-0AEBA5830172}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="63501" y="82550"/>
+          <a:ext cx="1054397" cy="1343025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1064,65 +1779,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="2:8" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="C3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="5" t="s">
         <v>89</v>
       </c>
+      <c r="G6" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1137,151 +1852,151 @@
       <c r="F7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="16" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="12" t="str">
+      <c r="G8" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-1_W2_ping_gateway.png", "Ver Evidencia PCWin11-1")</f>
         <v>Ver Evidencia PCWin11-1</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="12" t="str">
+      <c r="G9" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-1_W2_ping_gateway.png", "Ver Evidencia PCWin11-2")</f>
         <v>Ver Evidencia PCWin11-2</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="12" t="str">
+      <c r="G10" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-1_W3_ping_gateway.png", "Ver Evidencia PCWin11-3")</f>
         <v>Ver Evidencia PCWin11-3</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="16" t="s">
         <v>54</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="12" t="str">
+      <c r="G11" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-2_W1_ping_northbound.png", "Ver Evidencia PCWin11-1")</f>
         <v>Ver Evidencia PCWin11-1</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="12" t="str">
+      <c r="G12" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-2_W2_ping_northbound.png", "Ver Evidencia PCWin11-2")</f>
         <v>Ver Evidencia PCWin11-2</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="12" t="str">
+      <c r="G13" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-2_W3_ping_northbound.png", "Ver Evidencia PCWin11-3")</f>
         <v>Ver Evidencia PCWin11-3</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="12" t="str">
+      <c r="G14" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-3_W1_ping_nokia.png", "Ver Evidencia PCWin11-1")</f>
         <v>Ver Evidencia PCWin11-1</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="12" t="str">
+      <c r="G15" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-3_W2_ping_nokia.png", "Ver Evidencia PCWin11-2")</f>
         <v>Ver Evidencia PCWin11-2</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="12" t="str">
+      <c r="G16" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T1-3_W3_ping_nokia.png", "Ver Evidencia PCWin11-3")</f>
         <v>Ver Evidencia PCWin11-3</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1291,18 +2006,18 @@
         <v>17</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="12" t="str">
+      <c r="G17" s="7" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T2_docker_ps_galp.png", "Ver Evidencia Stack GLAP")</f>
         <v>Ver Evidencia Stack GLAP</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1315,15 +2030,15 @@
         <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="13" t="str">
+        <v>95</v>
+      </c>
+      <c r="G18" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T2-1_galp_targets_up.png", "Ver Evidencia Verificacion de servicios del stack")</f>
         <v>Ver Evidencia Verificacion de servicios del stack</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1338,13 +2053,13 @@
       <c r="F19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="13" t="str">
+      <c r="G19" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T3_suricata_zeek_docker_ps.png", "Ver Evidencia de activación de Zuticata y Zeek")</f>
         <v>Ver Evidencia de activación de Zuticata y Zeek</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1359,415 +2074,381 @@
       <c r="F20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="13" t="str">
+      <c r="G20" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T3-2_wazuh_docker_ps.png", "Ver Evidencia de activación servicios Wazuh")</f>
         <v>Ver Evidencia de activación servicios Wazuh</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="16" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="15" t="str">
+      <c r="G21" s="10" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T4_N1_ip_forward.png", "Ver Evidencia habilitacion del forwarding")</f>
         <v>Ver Evidencia habilitacion del forwarding</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="14"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="16" t="str">
+      <c r="G22" s="11" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T4_arp_initial.png", "Ver Evidencia MAC legitima del Gateway")</f>
         <v>Ver Evidencia MAC legitima del Gateway</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="16" t="str">
+      <c r="G23" s="11" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T4_N2_Envenenamiento.png", "Ver Evidencia envenenamiento (Arpsoof)")</f>
         <v>Ver Evidencia envenenamiento (Arpsoof)</v>
       </c>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="14"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
       <c r="E24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="16" t="str">
+        <v>96</v>
+      </c>
+      <c r="G24" s="11" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T4_arp_after_attack.png", "Ver Evidencia ARP después del ataque")</f>
         <v>Ver Evidencia ARP después del ataque</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="14"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
       <c r="E25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="16" t="str">
+      <c r="G25" s="11" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T4_N3_TCPDump.png", "Ver Evidencia aplicación del TCPDump")</f>
         <v>Ver Evidencia aplicación del TCPDump</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="13" t="str">
+        <v>75</v>
+      </c>
+      <c r="G26" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_ettercap_start.png", "Ver Evidencia iniciación del servicio spoofing")</f>
         <v>Ver Evidencia iniciación del servicio spoofing</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B27" s="14"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
       <c r="E27" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="13" t="str">
+        <v>73</v>
+      </c>
+      <c r="G27" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_ettercap_dns_plugin.png", "Ver Evidencia habilitación del plugin")</f>
         <v>Ver Evidencia habilitación del plugin</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="14"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="13" t="str">
+        <v>74</v>
+      </c>
+      <c r="G28" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_ettercap_hosts_scan.png", "Ver Evidencia selección del host")</f>
         <v>Ver Evidencia selección del host</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="14"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5" t="s">
-        <v>99</v>
+      <c r="B29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16" t="s">
+        <v>98</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="13" t="str">
+        <v>76</v>
+      </c>
+      <c r="G29" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_ettercap_arp_spoofing.png", "Ver Evidencia activación ARP Spoofing")</f>
         <v>Ver Evidencia activación ARP Spoofing</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="14"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="13" t="str">
+        <v>77</v>
+      </c>
+      <c r="G30" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_ettercap_attack_active.png", "Ver Evidencia del servicio activado")</f>
         <v>Ver Evidencia del servicio activado</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B31" s="14"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
       <c r="E31" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G31" s="13" t="str">
+        <v>78</v>
+      </c>
+      <c r="G31" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T5_victim_fake_site.png", "Ver Evidencia del sitio falso")</f>
         <v>Ver Evidencia del sitio falso</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G32" s="13" t="str">
+      <c r="F32" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T6_N1_GetService_Sysmon.png", "Ver Evidencia de GetService_Sysmon")</f>
         <v>Ver Evidencia de GetService_Sysmon</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="14"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="13" t="str">
+      <c r="B33" s="17"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T6_N2_AtaqueEjecutado.png", "Ver Evidencia del Ataque Ejecutado")</f>
         <v>Ver Evidencia del Ataque Ejecutado</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="14"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="13" t="str">
+      <c r="B34" s="17"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T6_N2_Hunting_Agente_Events.png", "Ver Evidencia del Hunting_Agente_Events.png")</f>
         <v>Ver Evidencia del Hunting_Agente_Events.png</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="C35" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="16" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G35" s="22" t="str">
+        <v>79</v>
+      </c>
+      <c r="G35" s="20" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T7_N1y2_AtacantayWhoami.png", "Ver Evidencia del Atacante y Whoami")</f>
         <v>Ver Evidencia del Atacante y Whoami</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="B36" s="14"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
       <c r="E36" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" s="22"/>
+        <v>80</v>
+      </c>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="2:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="14"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G37" s="13" t="str">
+      <c r="B37" s="17"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T7_N3_ComandoHydra.png", "Ver Evidencia del Comando Hydra")</f>
         <v>Ver Evidencia del Comando Hydra</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="14"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="13" t="str">
+      <c r="B38" s="17"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T7_N3_DashboardWazuh.png", "Ver Evidencia del Dashboard Wazuh")</f>
         <v>Ver Evidencia del Dashboard Wazuh</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G39" s="13" t="str">
+      <c r="G39" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T8_N1_Whoami_Hostname_Ipconfig.png", "Ver Evidencia del Whoami Hostname Ipconfig")</f>
         <v>Ver Evidencia del Whoami Hostname Ipconfig</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="14"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G40" s="13" t="str">
+      <c r="B40" s="17"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T8_N1_Detector_Eventos_Wazuh.png", "Ver Evidencia del Detector de Eventos de Wazuh")</f>
         <v>Ver Evidencia del Detector de Eventos de Wazuh</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="14"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="13" t="str">
+      <c r="B41" s="17"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T8_N1_Detector_Eventos_Wazuh_2.png", "Ver Evidencia del Detector de Eventos de Wazuh 2")</f>
         <v>Ver Evidencia del Detector de Eventos de Wazuh 2</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="C42" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G42" s="13" t="str">
+      <c r="G42" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T9_N1_Atacante.png", "Ver Evidencia del Atacante")</f>
         <v>Ver Evidencia del Atacante</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="14"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="13" t="str">
+      <c r="B43" s="17"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="8" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T9_N1_TableroWazuh_1.png", "Ver Evidencia del Tablero Wazuh 1")</f>
         <v>Ver Evidencia del Tablero Wazuh 1</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="23"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="21" t="str">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="14" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/T9_N1_TableroWazuh_2.png", "Ver Evidencia del Tablero Wazuh 2")</f>
         <v>Ver Evidencia del Tablero Wazuh 2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="B35:B38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="B21:B25"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="D26:D31"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C21:C25"/>
-    <mergeCell ref="D21:D25"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="C11:C13"/>
@@ -1777,6 +2458,40 @@
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C21:C25"/>
+    <mergeCell ref="D21:D25"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="D26:D31"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -1788,4 +2503,488 @@
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F7E5E5-952F-4BB4-8BF0-08E624E54E0C}">
+  <dimension ref="B1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" customWidth="1"/>
+    <col min="6" max="6" width="48.5703125" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+    </row>
+    <row r="2" spans="2:8" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="2:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-1_W1_ping_gateway.png", "Ver Evidencia PCWin11-1")</f>
+        <v>Ver Evidencia PCWin11-1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="24"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-1_W2_ping_gateway.png", "Ver Evidencia PCWin11-2")</f>
+        <v>Ver Evidencia PCWin11-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="24"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-1_W3_ping_gateway.png", "Ver Evidencia PCWin11-3")</f>
+        <v>Ver Evidencia PCWin11-3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-2_W1_ping_switch.png", "Ver Evidencia PCWin11-1")</f>
+        <v>Ver Evidencia PCWin11-1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="24"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-2_W2_ping_switch.png", "Ver Evidencia PCWin11-2")</f>
+        <v>Ver Evidencia PCWin11-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="24"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-2_W3_ping_switch.png", "Ver Evidencia PCWin11-3")</f>
+        <v>Ver Evidencia PCWin11-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-3_W1_ping_internet.png", "Ver Evidencia PCWin11-1")</f>
+        <v>Ver Evidencia PCWin11-1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="24"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-3_W2_ping_internet.png", "Ver Evidencia PCWin11-2")</f>
+        <v>Ver Evidencia PCWin11-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="24"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T1-3_W1_ping_internet.png", "Ver Evidencia PCWin11-3")</f>
+        <v>Ver Evidencia PCWin11-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="7" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T2_docker_ps.png", "Ver Evidencia Aplicaciones en Docker")</f>
+        <v>Ver Evidencia Aplicaciones en Docker</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B18" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T3_suricata.png", "Ver Evidencia de activación de Zuticata")</f>
+        <v>Ver Evidencia de activación de Zuticata</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G19" s="37" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_servidor.png", "Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento")</f>
+        <v>Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="41"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="37" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_maquina2.png", "Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1")</f>
+        <v>Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="41"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="37" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_naquina3.png", "Tablero 3: Panel -Evolución de Alertas- debe mostrar pico")</f>
+        <v>Tablero 3: Panel -Evolución de Alertas- debe mostrar pico</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="34" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G22" s="37" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_intentosSSH.png", "Tablero 2: Panel -Intentos SSH (R3) en Tiempo Real- debe mostrar pico")</f>
+        <v>Tablero 2: Panel -Intentos SSH (R3) en Tiempo Real- debe mostrar pico</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="41"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="37" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_alertacritica.png", "Tablero 2: Panel -Alertas Críticas (R6)- debe incrementar")</f>
+        <v>Tablero 2: Panel -Alertas Críticas (R6)- debe incrementar</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="41"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_Estado.png", "Tablero 4: Panel -Estado General de Seguridad- debe cambiar a ⚠️ o 🔴")</f>
+        <v>Tablero 4: Panel -Estado General de Seguridad- debe cambiar a ⚠️ o 🔴</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G25" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T6_MOvimientolateral.png", "Mensaje el grupo de Telegram")</f>
+        <v>Mensaje el grupo de Telegram</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="3" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G26" s="10" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T7_privilegios.png", "Segmento del Log")</f>
+        <v>Segmento del Log</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="29" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G27" s="11" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_telegramcombinado.png", "Mensaje el grupo de Telegram Alerta Crìtica")</f>
+        <v>Mensaje el grupo de Telegram Alerta Crìtica</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="48"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="11" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_PanelR6.png", "Tablero 2: Panel -R6 se incrementa")</f>
+        <v>Tablero 2: Panel -R6 se incrementa</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="49"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="11" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_EstadoCritico.png", "Tablero 4: Estado General cambia a crìtico")</f>
+        <v>Tablero 4: Estado General cambia a crìtico</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/protocolo_pruebas_WIP_v2_c.xlsx
+++ b/protocolo_pruebas_WIP_v2_c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LAC\2026\Sebastian\Tesis_pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB03F63E-D935-48CE-91A5-F066E890441A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B8C3A9-6580-4883-9B86-86197017B57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{63CCC3CA-1558-461E-B0B6-AA37C2AD9662}"/>
   </bookViews>
@@ -615,38 +615,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1.	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Instalar sshpass o usar WSL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2.	Intentar conexiones SSH con contraseñas incorrectas
-ssh usuario_inexistente@192.168.0.10
-ssh root@192.168.0.10
-ssh admin@192.168.0.10
-Repetir al menos 10 veces con diferentes usuarios
-for ($i=0; $i -le 10; $i++) {  ssh test$i@192.168.0.10}
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -668,23 +636,6 @@
       <t>)
 Demostrar que el sistema detecta ejecución remota de comandos desde una estación comprometida hacia otra.</t>
     </r>
-  </si>
-  <si>
-    <t>Desde PCW11-1 hacia PCW11-3</t>
-  </si>
-  <si>
-    <t>PCW11 - 1 
-Ejecutar comandos remotos en w3 (10.0.2.25)
-1.	Si tiene SSH habilitado en Windows:
-ssh win3@10.0.2.25 "whoami &amp;&amp; hostname &amp;&amp; ipconfig"
-2.	o usando PsExec (herramienta de Sysinternals)
-.\PsExec.exe \\10.0.2.25 -u win3 cmd /c "whoami"
-Acción desde w2 hacia Servidor
-Powershell: como Administrador en w2 (10.0.2.20)
-Múltiples conexiones SSH al servidor
-ssh win1@192.168.0.10 "ls -la /etc/"
-ssh win1@192.168.0.10 "cat /var/log/auth.log"
-ssh win1@192.168.0.10 "whoami"</t>
   </si>
   <si>
     <r>
@@ -711,9 +662,6 @@
     </r>
   </si>
   <si>
-    <t>Desde PCW11-3 hacia el servidor</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 1. 	Ver privilegios actuales
 whoami /priv
@@ -751,6 +699,34 @@
   </si>
   <si>
     <t>Acción coordinada desde PCW11_1 y PCW11-2 hacia el Servidor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.	Con  SSH
+2.	Intentar conexiones SSH con contraseñas incorrectas
+ssh usuario_inexistente@192.168.0.1
+ssh root@192.168.0.1
+ssh admin@192.168.0.1
+Repetir al menos 10 veces con diferentes usuarios
+for ($i=0; $i -le 10; $i++) {  ssh test$i@192.168.0.1}
+</t>
+  </si>
+  <si>
+    <t>Desde PCW11-1 hacia PCW11-2</t>
+  </si>
+  <si>
+    <t>PCW11 - 1 
+Ejecutar comandos remotos en PCW11-2 (192.168.0.95)
+1.	Si tiene SSH habilitado en Windows:
+ssh PCW11-2@192.168.0.95 "whoami &amp;&amp; hostname &amp;&amp; ipconfig"
+Acción desde PCW11-2 hacia Servidor
+Powershell: como Administrador en PCW11-2 (192.168.0.95)
+Múltiples conexiones SSH al servidor
+ssh win1@192.168.0.1 "ls -la /etc/"
+ssh win1@192.168.0.1 "cat /var/log/auth.log"
+ssh win1@192.168.0.1 "whoami"</t>
+  </si>
+  <si>
+    <t>Desde PCW11-3 hacia el PCW11-1</t>
   </si>
   <si>
     <r>
@@ -790,7 +766,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>for ($i=0; $i -le 15; $i++) { ssh usuario$i@192.168.0.10 }</t>
+      <t>for ($i=0; $i -le 15; $i++) { ssh usuario$i@192.168.0.1 }</t>
     </r>
   </si>
 </sst>
@@ -798,7 +774,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,15 +821,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,8 +847,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1080,17 +1061,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1101,7 +1071,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1185,12 +1155,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1206,9 +1176,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,34 +1185,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1766,7 +1745,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88F9D26C-F01D-4F0D-9B0D-9A3523484190}">
   <dimension ref="B1:I44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.140625" customWidth="1"/>
@@ -1775,7 +1754,8 @@
     <col min="5" max="5" width="38.28515625" customWidth="1"/>
     <col min="6" max="6" width="48.5703125" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" hidden="1"/>
+    <col min="10" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2507,8 +2487,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F7E5E5-952F-4BB4-8BF0-08E624E54E0C}">
-  <dimension ref="B1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.140625" customWidth="1"/>
@@ -2517,7 +2497,8 @@
     <col min="5" max="5" width="38.28515625" customWidth="1"/>
     <col min="6" max="6" width="48.5703125" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" hidden="1"/>
+    <col min="9" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2579,7 +2560,7 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="39" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -2597,7 +2578,7 @@
       <c r="G7" s="32"/>
     </row>
     <row r="8" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="49" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="16" t="s">
@@ -2618,7 +2599,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="24"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -2631,7 +2612,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="24"/>
+      <c r="B10" s="49"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
@@ -2644,7 +2625,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="49" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="16" t="s">
@@ -2665,7 +2646,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="24"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
@@ -2678,7 +2659,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="24"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -2691,7 +2672,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="49" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="16" t="s">
@@ -2712,7 +2693,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="24"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
@@ -2725,7 +2706,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="24"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
@@ -2738,7 +2719,7 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -2759,7 +2740,7 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="40" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -2779,7 +2760,7 @@
         <v>Ver Evidencia de activación de Zuticata</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="41" t="s">
         <v>33</v>
       </c>
@@ -2795,186 +2776,224 @@
       <c r="F19" s="33" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="G19" s="37" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_servidor.png", "Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento")</f>
-        <v>Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="36" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_ETSCAN.png", "Alertas Even_json")</f>
+        <v>Alertas Even_json</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="41"/>
       <c r="C20" s="16"/>
       <c r="D20" s="33"/>
       <c r="E20" s="27"/>
       <c r="F20" s="33"/>
-      <c r="G20" s="37" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_maquina2.png", "Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1")</f>
-        <v>Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20" s="36" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_Wazuh.png", "Alertas Wazuh")</f>
+        <v>Alertas Wazuh</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="41"/>
       <c r="C21" s="16"/>
       <c r="D21" s="33"/>
-      <c r="E21" s="28"/>
+      <c r="E21" s="27"/>
       <c r="F21" s="33"/>
-      <c r="G21" s="37" t="str">
+      <c r="G21" s="36" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_servidor.png", "Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento")</f>
+        <v>Tablero 2: Panel - Alertas R1-R6 por hora - debe mostrar incremento</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="41"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="36" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_maquina2.png", "Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1")</f>
+        <v>Tablero 3: Panel -Top 10 IPs Atacantes- debe mostrar PCW11-1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="41"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="36" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T4_naquina3.png", "Tablero 3: Panel -Evolución de Alertas- debe mostrar pico")</f>
         <v>Tablero 3: Panel -Evolución de Alertas- debe mostrar pico</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="41" t="s">
+    <row r="24" spans="2:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C24" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D24" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="E22" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="34" t="e" vm="2">
+      <c r="E24" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="34" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G22" s="37" t="str">
+      <c r="G24" s="36" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_intentosSSH.png", "Tablero 2: Panel -Intentos SSH (R3) en Tiempo Real- debe mostrar pico")</f>
         <v>Tablero 2: Panel -Intentos SSH (R3) en Tiempo Real- debe mostrar pico</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="41"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="37" t="str">
+    <row r="25" spans="2:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="41"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="36" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_alertacritica.png", "Tablero 2: Panel -Alertas Críticas (R6)- debe incrementar")</f>
         <v>Tablero 2: Panel -Alertas Críticas (R6)- debe incrementar</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="41"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="8" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_Estado.png", "Tablero 4: Panel -Estado General de Seguridad- debe cambiar a ⚠️ o 🔴")</f>
-        <v>Tablero 4: Panel -Estado General de Seguridad- debe cambiar a ⚠️ o 🔴</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="13" t="s">
+    <row r="26" spans="2:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="41"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="8" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_Estado.png", "Tablero 4: Panel -Estado General de Seguridad- debe cambiar")</f>
+        <v>Tablero 4: Panel -Estado General de Seguridad- debe cambiar</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C27" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="29" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G27" s="46" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_PC1_PC2.png", "SSH del PCW11-1 a PCW11_2")</f>
+        <v>SSH del PCW11-1 a PCW11_2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="48"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="47" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_WazuhPC2.png", "Alerta Wazuh entrada a PCW!!-2")</f>
+        <v>Alerta Wazuh entrada a PCW!!-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="48"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="46" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T5_Telegram_1.png", "Mensaje Telegram Fuerza Bruta")</f>
+        <v>Mensaje Telegram Fuerza Bruta</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="282" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="F30" s="3" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G30" s="10" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T7_privilegios.png", "Visor de eventos de Wazuh")</f>
+        <v>Visor de eventos de Wazuh</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="F25" s="3" t="e" vm="3">
+      <c r="D31" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="30" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="G25" s="8" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T6_MOvimientolateral.png", "Mensaje el grupo de Telegram")</f>
-        <v>Mensaje el grupo de Telegram</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="3" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G26" s="10" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T7_privilegios.png", "Segmento del Log")</f>
-        <v>Segmento del Log</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="29" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G27" s="11" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_telegramcombinado.png", "Mensaje el grupo de Telegram Alerta Crìtica")</f>
-        <v>Mensaje el grupo de Telegram Alerta Crìtica</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="48"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="11" t="str">
-        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_PanelR6.png", "Tablero 2: Panel -R6 se incrementa")</f>
-        <v>Tablero 2: Panel -R6 se incrementa</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="49"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="11" t="str">
+      <c r="G31" s="11" t="str">
+        <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_20alertas.png", "Tablero 2: Log últimas 20 Alertas")</f>
+        <v>Tablero 2: Log últimas 20 Alertas</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="52"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="11" t="str">
         <f>HYPERLINK("https://github.com/jclavijomartinez/tesis/blob/main/imagenes/F2T8_EstadoCritico.png", "Tablero 4: Estado General cambia a crìtico")</f>
         <v>Tablero 4: Estado General cambia a crìtico</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="35">
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="F27:F29"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="F19:F23"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
     <mergeCell ref="E8:E10"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="E14:E16"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="D19:D23"/>
+    <mergeCell ref="E19:E23"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="D8:D10"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="C11:C13"/>
     <mergeCell ref="D11:D13"/>
@@ -2985,6 +3004,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>